--- a/p6_deployment/data/spain/predicciones.xlsx
+++ b/p6_deployment/data/spain/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.66666666666</v>
+        <v>45519.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,65 +594,763 @@
       <c r="F2" t="n">
         <v>1481</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J2" t="n">
         <v>4.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6499535747446611</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2243887341380377</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1256576911173011</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06108374384236459</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3805268049760931</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.345111177425761</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2743620175981458</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.2694267697685679</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.2694267697685679</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6194731950239069</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.692307692307693</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>49.55785560191255</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>49.55785560191255</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>148</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3505154639175257</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2783505154639175</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3711340206185567</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05664488017429203</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3452293726455771</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.3289246424939313</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3258459848604917</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.005286091271948623</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.005286091271948623</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3452293726455771</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>27.61834981164617</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>27.61834981164617</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>148</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.2246112923145128</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.2300896165173058</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5452990911681813</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.06003235920055339</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L4" t="n">
+        <v>0.4839055793991416</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2859442060085837</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2301502145922747</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05975325487520622</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3318740458112689</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.359411467355663</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.308714486833068</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.07346726134707932</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.07346726134707932</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.359411467355663</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>28.75291738845304</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>28.75291738845304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>148</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3306780664681976</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3072105907833578</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3621113427484446</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05003100426564178</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>0.08310156928837978</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2188273457344095</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.6980710849772107</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0.1527719938090294</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="Q5" t="n">
+        <v>0.2439626972668601</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3475270623489908</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4085102403841492</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.04639889763570459</v>
+      </c>
+      <c r="V5" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
-        <v>0.1527719938090294</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6980710849772107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>55.84568679817686</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>55.84568679817686</v>
+      <c r="W5" t="n">
+        <v>0.04639889763570459</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4085102403841492</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>32.68081923073193</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>32.68081923073193</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>148</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5657460116663153</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2699416684236418</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1643123199100429</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05842972440212746</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3124549235379637</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3522409161091845</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3353041603528517</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.08229924768554264</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.08229924768554264</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3522409161091845</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>28.17927328873476</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>28.17927328873476</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2102766798418972</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2490118577075099</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5407114624505929</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05680868838763575</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.09985275475641719</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3537311703286375</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5464160749149451</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.005704612464352277</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.005704612464352277</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5464160749149451</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>43.71328599319561</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>43.71328599319561</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6107906345436037</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2629793009840516</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1262300644723447</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05627240143369172</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4786041049543034</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3578703820955491</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1635255129501476</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.1321865295893003</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.1321865295893003</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4786041049543034</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>38.28832839634427</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>38.28832839634427</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.181119109947644</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2319208115183246</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5869600785340313</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05166258011786473</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1105832018738358</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.341123587151023</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5482932109751412</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.03866686755889015</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.03866686755889015</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5482932109751412</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>43.86345687801129</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>43.86345687801129</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/predicciones.xlsx
+++ b/p6_deployment/data/spain/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3805268049760931</v>
+        <v>0.3864291983857749</v>
       </c>
       <c r="R2" t="n">
-        <v>0.345111177425761</v>
+        <v>0.344609510426887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2743620175981458</v>
+        <v>0.2689612911873382</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2694267697685679</v>
+        <v>-0.2635243763588862</v>
       </c>
       <c r="V2" t="n">
         <v>-1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2694267697685679</v>
+        <v>0.2635243763588862</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6194731950239069</v>
+        <v>0.6135708016142252</v>
       </c>
       <c r="Y2" t="n">
         <v>2.692307692307693</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>49.55785560191255</v>
+        <v>49.08566412913801</v>
       </c>
       <c r="AB2" t="n">
-        <v>49.55785560191255</v>
+        <v>49.08566412913801</v>
       </c>
     </row>
     <row r="3">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="M3" t="n">
         <v>0.2783505154639175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="O3" t="n">
         <v>0.05664488017429203</v>
@@ -727,31 +727,31 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3452293726455771</v>
+        <v>0.3459842340935354</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3289246424939313</v>
+        <v>0.3293307959243996</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3258459848604917</v>
+        <v>0.3246849699820651</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.005286091271948623</v>
+        <v>-0.02514978652502131</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.005286091271948623</v>
+        <v>-0.02514978652502131</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3452293726455771</v>
+        <v>0.3459842340935354</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>27.61834981164617</v>
+        <v>27.67873872748283</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.61834981164617</v>
+        <v>27.67873872748283</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3318740458112689</v>
+        <v>0.331107464233866</v>
       </c>
       <c r="R4" t="n">
-        <v>0.359411467355663</v>
+        <v>0.3594350691873274</v>
       </c>
       <c r="S4" t="n">
-        <v>0.308714486833068</v>
+        <v>0.3094574665788066</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07346726134707932</v>
+        <v>0.0734908631787437</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07346726134707932</v>
+        <v>0.0734908631787437</v>
       </c>
       <c r="X4" t="n">
-        <v>0.359411467355663</v>
+        <v>0.3594350691873274</v>
       </c>
       <c r="Y4" t="n">
         <v>3.3</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>28.75291738845304</v>
+        <v>28.75480553498619</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.75291738845304</v>
+        <v>28.75480553498619</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2439626972668601</v>
+        <v>0.246931330001923</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3475270623489908</v>
+        <v>0.348392975313419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4085102403841492</v>
+        <v>0.404675694684658</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04639889763570459</v>
+        <v>0.04256435193621338</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04639889763570459</v>
+        <v>0.04256435193621338</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4085102403841492</v>
+        <v>0.404675694684658</v>
       </c>
       <c r="Y5" t="n">
         <v>2.63</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>32.68081923073193</v>
+        <v>32.37405557477264</v>
       </c>
       <c r="AB5" t="n">
-        <v>32.68081923073193</v>
+        <v>32.37405557477264</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3124549235379637</v>
+        <v>0.3130417256142337</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3522409161091845</v>
+        <v>0.3517999519823501</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3353041603528517</v>
+        <v>0.3351583224034164</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08229924768554264</v>
+        <v>0.08185828355870828</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08229924768554264</v>
+        <v>0.08185828355870828</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3522409161091845</v>
+        <v>0.3517999519823501</v>
       </c>
       <c r="Y6" t="n">
         <v>3.5</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>28.17927328873476</v>
+        <v>28.14399615858801</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.17927328873476</v>
+        <v>28.14399615858801</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09985275475641719</v>
+        <v>0.111303398903951</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3537311703286375</v>
+        <v>0.3584747258018501</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5464160749149451</v>
+        <v>0.5302218752941988</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005704612464352277</v>
+        <v>-0.01048958715639403</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005704612464352277</v>
+        <v>-0.01048958715639403</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5464160749149451</v>
+        <v>0.5302218752941988</v>
       </c>
       <c r="Y7" t="n">
         <v>1.75</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>43.71328599319561</v>
+        <v>42.41775002353591</v>
       </c>
       <c r="AB7" t="n">
-        <v>43.71328599319561</v>
+        <v>42.41775002353591</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4786041049543034</v>
+        <v>0.4774742622387215</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3578703820955491</v>
+        <v>0.3570346095325539</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1635255129501476</v>
+        <v>0.1654911282287247</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1321865295893003</v>
+        <v>-0.1333163723048822</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1321865295893003</v>
+        <v>-0.1333163723048822</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4786041049543034</v>
+        <v>0.4774742622387215</v>
       </c>
       <c r="Y8" t="n">
         <v>1.55</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>38.28832839634427</v>
+        <v>38.19794097909772</v>
       </c>
       <c r="AB8" t="n">
-        <v>38.28832839634427</v>
+        <v>38.19794097909772</v>
       </c>
     </row>
     <row r="9">
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.181119109947644</v>
+        <v>0.1740031071983429</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2319208115183246</v>
+        <v>0.2278612118073537</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5869600785340313</v>
+        <v>0.5981356809943036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05166258011786473</v>
+        <v>0.04491341991341979</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1105832018738358</v>
+        <v>0.1178914627609569</v>
       </c>
       <c r="R9" t="n">
-        <v>0.341123587151023</v>
+        <v>0.3452121719028504</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5482932109751412</v>
+        <v>0.5368963653361926</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.03866686755889015</v>
+        <v>-0.06123931565811103</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03866686755889015</v>
+        <v>-0.06123931565811103</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5482932109751412</v>
+        <v>0.5368963653361926</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,362 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>43.86345687801129</v>
+        <v>42.9517092268954</v>
       </c>
       <c r="AB9" t="n">
-        <v>43.86345687801129</v>
+        <v>42.9517092268954</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3961661341853036</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3067092651757188</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2971246006389776</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.051747311827957</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.365759141906339</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3169466070438444</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3172942510498165</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.03040699227896454</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.03040699227896454</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.365759141906339</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>29.26073135250712</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>29.26073135250712</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3165610142630745</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2793185419968304</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4041204437400951</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05298289528577382</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2287261327627184</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.321274277708838</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4499995895284436</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.04587914578834851</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.04587914578834851</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.4499995895284436</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>35.99996716227549</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>35.99996716227549</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.254701932172643</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2699619381061662</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4753361297211908</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.5246638702788091</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>41.97310962230473</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>41.97310962230473</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.580908140317435</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2584388634523319</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1606529962302331</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.419091859682565</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.2</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>33.5273487746052</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>33.5273487746052</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/predicciones.xlsx
+++ b/p6_deployment/data/spain/predicciones.xlsx
@@ -626,45 +626,45 @@
         <v>0.06108374384236459</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3864291983857749</v>
+        <v>0.3601129423751186</v>
       </c>
       <c r="R2" t="n">
-        <v>0.344609510426887</v>
+        <v>0.3853165190115848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2689612911873382</v>
+        <v>0.2545705386132965</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2635243763588862</v>
+        <v>0.160927784873547</v>
       </c>
       <c r="V2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2635243763588862</v>
+        <v>0.160927784873547</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6135708016142252</v>
+        <v>0.3853165190115848</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.692307692307693</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>49.08566412913801</v>
+        <v>7.884542645647259</v>
       </c>
       <c r="AB2" t="n">
-        <v>49.08566412913801</v>
+        <v>7.884542645647259</v>
       </c>
     </row>
     <row r="3">
@@ -724,45 +724,45 @@
         <v>0.05664488017429203</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3459842340935354</v>
+        <v>0.3005982888732319</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3293307959243996</v>
+        <v>0.3561749885481319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3246849699820651</v>
+        <v>0.3432267225786362</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.02514978652502131</v>
+        <v>0.07782447308421436</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.02514978652502131</v>
+        <v>0.07782447308421436</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3459842340935354</v>
+        <v>0.3561749885481319</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>27.67873872748283</v>
+        <v>7.288233823259048</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.67873872748283</v>
+        <v>7.288233823259048</v>
       </c>
     </row>
     <row r="4">
@@ -825,42 +825,42 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.331107464233866</v>
+        <v>0.3622449865343431</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3594350691873274</v>
+        <v>0.3879840373722267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3094574665788066</v>
+        <v>0.2497709760934302</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0734908631787437</v>
+        <v>0.102039831363643</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0734908631787437</v>
+        <v>0.102039831363643</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3594350691873274</v>
+        <v>0.3879840373722267</v>
       </c>
       <c r="Y4" t="n">
         <v>3.3</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>28.75480553498619</v>
+        <v>7.939126763469356</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.75480553498619</v>
+        <v>7.939126763469356</v>
       </c>
     </row>
     <row r="5">
@@ -923,42 +923,42 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.246931330001923</v>
+        <v>0.2473357881187033</v>
       </c>
       <c r="R5" t="n">
-        <v>0.348392975313419</v>
+        <v>0.3659811447793581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.404675694684658</v>
+        <v>0.3866830671019386</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04256435193621338</v>
+        <v>0.02457172435349397</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04256435193621338</v>
+        <v>0.02457172435349397</v>
       </c>
       <c r="X5" t="n">
-        <v>0.404675694684658</v>
+        <v>0.3866830671019386</v>
       </c>
       <c r="Y5" t="n">
         <v>2.63</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>32.37405557477264</v>
+        <v>7.912505647917085</v>
       </c>
       <c r="AB5" t="n">
-        <v>32.37405557477264</v>
+        <v>7.912505647917085</v>
       </c>
     </row>
     <row r="6">
@@ -1017,47 +1017,29 @@
       <c r="O6" t="n">
         <v>0.05842972440212746</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3130417256142337</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3517999519823501</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3351583224034164</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.08185828355870828</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.08185828355870828</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.3517999519823501</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>1.294137466307278</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>28.14399615858801</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>28.14399615858801</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1119,42 +1101,42 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.111303398903951</v>
+        <v>0.200172865846591</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3584747258018501</v>
+        <v>0.335690311794075</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5302218752941988</v>
+        <v>0.4641368223593341</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01048958715639403</v>
+        <v>-0.07657464009125881</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01048958715639403</v>
+        <v>-0.07657464009125881</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5302218752941988</v>
+        <v>0.4641368223593341</v>
       </c>
       <c r="Y7" t="n">
         <v>1.75</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>42.41775002353591</v>
+        <v>9.497403793366436</v>
       </c>
       <c r="AB7" t="n">
-        <v>42.41775002353591</v>
+        <v>9.497403793366436</v>
       </c>
     </row>
     <row r="8">
@@ -1217,42 +1199,42 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4774742622387215</v>
+        <v>0.4307893898699516</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3570346095325539</v>
+        <v>0.3702355820916102</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1654911282287247</v>
+        <v>0.1989750280384382</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1333163723048822</v>
+        <v>-0.1800012446736521</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1333163723048822</v>
+        <v>-0.1800012446736521</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4774742622387215</v>
+        <v>0.4307893898699516</v>
       </c>
       <c r="Y8" t="n">
         <v>1.55</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>38.19794097909772</v>
+        <v>8.81503166392894</v>
       </c>
       <c r="AB8" t="n">
-        <v>38.19794097909772</v>
+        <v>8.81503166392894</v>
       </c>
     </row>
     <row r="9">
@@ -1315,42 +1297,42 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1178914627609569</v>
+        <v>0.1447198562477187</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3452121719028504</v>
+        <v>0.3361782388442547</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5368963653361926</v>
+        <v>0.5191019049080265</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06123931565811103</v>
+        <v>-0.07903377608627704</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06123931565811103</v>
+        <v>-0.07903377608627704</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5368963653361926</v>
+        <v>0.5191019049080265</v>
       </c>
       <c r="Y9" t="n">
         <v>1.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>42.9517092268954</v>
+        <v>10.62212727651318</v>
       </c>
       <c r="AB9" t="n">
-        <v>42.9517092268954</v>
+        <v>10.62212727651318</v>
       </c>
     </row>
     <row r="10">
@@ -1409,47 +1391,29 @@
       <c r="O10" t="n">
         <v>0.051747311827957</v>
       </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.365759141906339</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3169466070438444</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3172942510498165</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>-0.03040699227896454</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.03040699227896454</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.365759141906339</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>2.4</v>
+        <v>1.371428571428572</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
-        </is>
-      </c>
-      <c r="AA10" t="n">
-        <v>29.26073135250712</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>29.26073135250712</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1487,66 +1451,66 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2287261327627184</v>
+        <v>0.2392809304111867</v>
       </c>
       <c r="R11" t="n">
-        <v>0.321274277708838</v>
+        <v>0.3452281670202072</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4499995895284436</v>
+        <v>0.4154909025686062</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04587914578834851</v>
+        <v>0.02657994856113938</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04587914578834851</v>
+        <v>0.02657994856113938</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4499995895284436</v>
+        <v>0.4154909025686062</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>35.99996716227549</v>
+        <v>8.50198623351041</v>
       </c>
       <c r="AB11" t="n">
-        <v>35.99996716227549</v>
+        <v>8.50198623351041</v>
       </c>
     </row>
     <row r="12">
@@ -1595,13 +1559,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.254701932172643</v>
+        <v>0.3402714508527864</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2699619381061662</v>
+        <v>0.2425388254299746</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4753361297211908</v>
+        <v>0.417189723717239</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1612,19 +1576,19 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.5246638702788091</v>
+        <v>0.5828102762827609</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.2</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>41.97310962230473</v>
+        <v>11.92576038385402</v>
       </c>
       <c r="AB12" t="n">
-        <v>41.97310962230473</v>
+        <v>11.92576038385402</v>
       </c>
     </row>
     <row r="13">
@@ -1673,13 +1637,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.580908140317435</v>
+        <v>0.3947548278277958</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2584388634523319</v>
+        <v>0.2455254570053078</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1606529962302331</v>
+        <v>0.3597197151668962</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1690,19 +1654,19 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0.419091859682565</v>
+        <v>0.6052451721722042</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.2</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>33.5273487746052</v>
+        <v>12.38483463752144</v>
       </c>
       <c r="AB13" t="n">
-        <v>33.5273487746052</v>
+        <v>12.38483463752144</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/predicciones.xlsx
+++ b/p6_deployment/data/spain/predicciones.xlsx
@@ -626,45 +626,45 @@
         <v>0.06108374384236459</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3601129423751186</v>
+        <v>0.3543207301500569</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3853165190115848</v>
+        <v>0.3309504969275024</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2545705386132965</v>
+        <v>0.3147287729224407</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.160927784873547</v>
+        <v>-0.2956328445946042</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.160927784873547</v>
+        <v>0.2956328445946042</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3853165190115848</v>
+        <v>0.6456792698499432</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>2.692307692307693</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>7.884542645647259</v>
+        <v>9.885606821282982</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.884542645647259</v>
+        <v>9.885606821282982</v>
       </c>
     </row>
     <row r="3">
@@ -703,66 +703,66 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3005982888732319</v>
+        <v>0.3450016956237524</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3561749885481319</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3432267225786362</v>
+        <v>0.2835960499940407</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07782447308421436</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07782447308421436</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3561749885481319</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="Y3" t="n">
         <v>3.4</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>7.288233823259048</v>
+        <v>5.686316458965599</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.288233823259048</v>
+        <v>5.686316458965599</v>
       </c>
     </row>
     <row r="4">
@@ -825,42 +825,42 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3622449865343431</v>
+        <v>0.2917897629546954</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3879840373722267</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2497709760934302</v>
+        <v>0.3523444024590837</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.102039831363643</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.102039831363643</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3879840373722267</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="Y4" t="n">
         <v>3.3</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>7.939126763469356</v>
+        <v>5.448447683111589</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.939126763469356</v>
+        <v>5.448447683111589</v>
       </c>
     </row>
     <row r="5">
@@ -923,42 +923,42 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2473357881187033</v>
+        <v>0.1663911399929355</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3659811447793581</v>
+        <v>0.3464497059716086</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3866830671019386</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02457172435349397</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02457172435349397</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3866830671019386</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="Y5" t="n">
         <v>2.63</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>7.912505647917085</v>
+        <v>7.458600703260249</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.912505647917085</v>
+        <v>7.458600703260249</v>
       </c>
     </row>
     <row r="6">
@@ -1017,29 +1017,47 @@
       <c r="O6" t="n">
         <v>0.05842972440212746</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4014381059865235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3129428747972791</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2856190192161973</v>
+      </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>-0.1643079056797918</v>
+      </c>
       <c r="V6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1643079056797918</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5985618940134765</v>
+      </c>
       <c r="Y6" t="n">
-        <v>1.294137466307278</v>
+        <v>2.175675675675676</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.164221028491188</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.164221028491188</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1101,42 +1119,42 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.200172865846591</v>
+        <v>0.08782328920802665</v>
       </c>
       <c r="R7" t="n">
-        <v>0.335690311794075</v>
+        <v>0.3046577231035404</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4641368223593341</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07657464009125881</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.07657464009125881</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4641368223593341</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="Y7" t="n">
         <v>1.75</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>9.497403793366436</v>
+        <v>9.301357700623464</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.497403793366436</v>
+        <v>9.301357700623464</v>
       </c>
     </row>
     <row r="8">
@@ -1199,42 +1217,42 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4307893898699516</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3702355820916102</v>
+        <v>0.2831583750474474</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1989750280384382</v>
+        <v>0.1639463079895984</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1800012446736521</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1800012446736521</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4307893898699516</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="Y8" t="n">
         <v>1.55</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>8.81503166392894</v>
+        <v>8.465047543023386</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.81503166392894</v>
+        <v>8.465047543023386</v>
       </c>
     </row>
     <row r="9">
@@ -1297,42 +1315,42 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1447198562477187</v>
+        <v>0.08103257282901304</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3361782388442547</v>
+        <v>0.2903271265316048</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5191019049080265</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07903377608627704</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.07903377608627704</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5191019049080265</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="Y9" t="n">
         <v>1.6</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>10.62212727651318</v>
+        <v>9.624733415366299</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.62212727651318</v>
+        <v>9.624733415366299</v>
       </c>
     </row>
     <row r="10">
@@ -1391,29 +1409,47 @@
       <c r="O10" t="n">
         <v>0.051747311827957</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3609999082839134</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3275469899490511</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3114531017670354</v>
+      </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
       <c r="V10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.3609999082839134</v>
+      </c>
       <c r="Y10" t="n">
-        <v>1.371428571428572</v>
+        <v>2.4</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.52705239653018</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.52705239653018</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1451,66 +1487,66 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2392809304111867</v>
+        <v>0.2799751019411993</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3452281670202072</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4154909025686062</v>
+        <v>0.3551977642422137</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02657994856113938</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02657994856113938</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4154909025686062</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>8.50198623351041</v>
+        <v>5.585648743972431</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.50198623351041</v>
+        <v>5.585648743972431</v>
       </c>
     </row>
     <row r="12">
@@ -1559,13 +1595,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3402714508527864</v>
+        <v>0.1838937751487623</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2425388254299746</v>
+        <v>0.2459078968870776</v>
       </c>
       <c r="S12" t="n">
-        <v>0.417189723717239</v>
+        <v>0.57019832796416</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1576,19 +1612,19 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.5828102762827609</v>
+        <v>0.42980167203584</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>11.92576038385402</v>
+        <v>6.580434806066749</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.92576038385402</v>
+        <v>6.580434806066749</v>
       </c>
     </row>
     <row r="13">
@@ -1637,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3947548278277958</v>
+        <v>0.7540168523407008</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2455254570053078</v>
+        <v>0.131951511035547</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3597197151668962</v>
+        <v>0.1140316366237523</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1654,19 +1690,19 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0.6052451721722042</v>
+        <v>0.2459831476592992</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>12.38483463752144</v>
+        <v>3.766099975590909</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.38483463752144</v>
+        <v>3.766099975590909</v>
       </c>
     </row>
   </sheetData>
